--- a/2026/TUCUMAN 1061/Marzo/tucuman Marzo.xlsx
+++ b/2026/TUCUMAN 1061/Marzo/tucuman Marzo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\TUCUMAN 1061\Marzo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\TUCUMAN 1061\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7A30EF-52CB-450B-93A0-E359A9378288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992534D1-1E93-433F-AD31-945ADA0A8544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gastos" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Calculo Servicios  (2)'!$A$6:$H$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$2:$H$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$2:$H$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$P$39</definedName>
     <definedName name="CantOper" localSheetId="2">#REF!</definedName>
     <definedName name="CantOper">#REF!</definedName>
@@ -36,6 +36,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -66,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="161">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -554,7 +557,7 @@
     <t>Administraciòn MARZO 2025:</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
+    <t>Traspaso admiistracion</t>
   </si>
 </sst>
 </file>
@@ -1371,7 +1374,7 @@
     <xf numFmtId="167" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="272">
+  <cellXfs count="271">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -1893,7 +1896,6 @@
     <xf numFmtId="1" fontId="25" fillId="8" borderId="29" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="34" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2237,14 +2239,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:N54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2257,7 +2259,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="D3" s="9" t="s">
         <v>1</v>
@@ -2268,7 +2270,7 @@
       <c r="F3" s="199"/>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="D4" s="9" t="s">
         <v>2</v>
@@ -2278,7 +2280,7 @@
       </c>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="D5" t="s">
         <v>17</v>
@@ -2286,7 +2288,7 @@
       <c r="H5" s="5"/>
       <c r="J5" s="152"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="D6" s="200" t="s">
         <v>143</v>
@@ -2296,7 +2298,7 @@
       <c r="G6" s="200"/>
       <c r="H6" s="201"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="D7" s="200"/>
       <c r="E7" s="200"/>
@@ -2304,7 +2306,7 @@
       <c r="G7" s="200"/>
       <c r="H7" s="201"/>
     </row>
-    <row r="8" spans="1:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="D8" s="200"/>
       <c r="E8" s="200"/>
@@ -2312,7 +2314,7 @@
       <c r="G8" s="200"/>
       <c r="H8" s="201"/>
     </row>
-    <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>3</v>
       </c>
@@ -2328,7 +2330,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -2338,11 +2340,11 @@
       <c r="G10" s="1"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>4</v>
       </c>
@@ -2351,7 +2353,7 @@
       </c>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="181"/>
       <c r="B13" s="182"/>
       <c r="C13" s="182"/>
@@ -2361,7 +2363,7 @@
       <c r="G13" s="182"/>
       <c r="H13" s="183"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="213" t="s">
         <v>11</v>
       </c>
@@ -2373,7 +2375,7 @@
       <c r="G14" s="213"/>
       <c r="H14" s="213"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="184"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -2383,7 +2385,7 @@
       <c r="G15" s="14"/>
       <c r="H15" s="185"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>46</v>
       </c>
@@ -2400,7 +2402,7 @@
         <v>400115.4</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="187" t="s">
         <v>158</v>
       </c>
@@ -2414,7 +2416,7 @@
         <v>4030.28</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="188" t="s">
         <v>5</v>
       </c>
@@ -2429,7 +2431,7 @@
         <v>404145.68000000005</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="181"/>
       <c r="B19" s="182"/>
       <c r="C19" s="182"/>
@@ -2439,7 +2441,7 @@
       <c r="G19" s="182"/>
       <c r="H19" s="183"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="214" t="s">
         <v>6</v>
       </c>
@@ -2451,7 +2453,7 @@
       <c r="G20" s="215"/>
       <c r="H20" s="216"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="184" t="s">
         <v>45</v>
       </c>
@@ -2461,11 +2463,11 @@
       <c r="E21" s="14"/>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
-      <c r="H21" s="271">
+      <c r="H21" s="15">
         <v>18355.59</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="184" t="s">
         <v>44</v>
       </c>
@@ -2476,10 +2478,10 @@
       <c r="F22" s="14"/>
       <c r="G22" s="14"/>
       <c r="H22" s="15">
-        <v>974869.58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1143139.0900000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>7</v>
       </c>
@@ -2491,10 +2493,10 @@
       <c r="G23" s="189"/>
       <c r="H23" s="192">
         <f>SUM(H21:H22)</f>
-        <v>993225.16999999993</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1161494.6800000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="213" t="s">
         <v>47</v>
       </c>
@@ -2507,7 +2509,7 @@
       <c r="H24" s="213"/>
       <c r="J24" s="15"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="187" t="s">
         <v>148</v>
       </c>
@@ -2523,97 +2525,99 @@
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="187" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="B26" s="14"/>
-      <c r="C26" s="191"/>
+      <c r="C26" s="14"/>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
-      <c r="H26" s="271">
-        <v>32650</v>
-      </c>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="187" t="s">
+      <c r="H26" s="15">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="188" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="189"/>
+      <c r="C27" s="189"/>
+      <c r="D27" s="189"/>
+      <c r="E27" s="189"/>
+      <c r="F27" s="189"/>
+      <c r="G27" s="189"/>
+      <c r="H27" s="192">
+        <f>SUM(H25:H26)</f>
+        <v>128099.51999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="214" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="215"/>
+      <c r="C28" s="215"/>
+      <c r="D28" s="215"/>
+      <c r="E28" s="215"/>
+      <c r="F28" s="215"/>
+      <c r="G28" s="215"/>
+      <c r="H28" s="216"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="184" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="193">
+        <v>97600</v>
+      </c>
+      <c r="I29" s="28"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="184" t="s">
         <v>160</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="191"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="271">
-        <v>65450</v>
-      </c>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-    </row>
-    <row r="28" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="187" t="s">
-        <v>128</v>
-      </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="271">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="188" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="189"/>
-      <c r="C29" s="189"/>
-      <c r="D29" s="189"/>
-      <c r="E29" s="189"/>
-      <c r="F29" s="189"/>
-      <c r="G29" s="189"/>
-      <c r="H29" s="192">
-        <f>SUM(H25:H28)</f>
-        <v>226199.52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="214" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="215"/>
-      <c r="C30" s="215"/>
-      <c r="D30" s="215"/>
-      <c r="E30" s="215"/>
-      <c r="F30" s="215"/>
-      <c r="G30" s="215"/>
-      <c r="H30" s="216"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="184" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="193">
-        <v>97600</v>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="193">
+        <v>200000</v>
+      </c>
+      <c r="I30" s="28"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="188" t="s">
+        <v>159</v>
+      </c>
+      <c r="B31" s="189"/>
+      <c r="C31" s="189"/>
+      <c r="D31" s="189"/>
+      <c r="E31" s="189"/>
+      <c r="F31" s="189"/>
+      <c r="G31" s="189"/>
+      <c r="H31" s="194">
+        <f>SUM(H29:H30)</f>
+        <v>297600</v>
       </c>
       <c r="I31" s="28"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N31" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="184"/>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -2621,174 +2625,167 @@
       <c r="E32" s="14"/>
       <c r="F32" s="14"/>
       <c r="G32" s="14"/>
-      <c r="H32" s="193">
-        <v>0</v>
-      </c>
-      <c r="I32" s="28"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="188" t="s">
-        <v>159</v>
-      </c>
-      <c r="B33" s="189"/>
-      <c r="C33" s="189"/>
-      <c r="D33" s="189"/>
-      <c r="E33" s="189"/>
-      <c r="F33" s="189"/>
-      <c r="G33" s="189"/>
-      <c r="H33" s="194">
-        <f>SUM(H31:H32)</f>
-        <v>97600</v>
-      </c>
-      <c r="I33" s="28"/>
-      <c r="N33" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="184"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="195"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="214" t="s">
+      <c r="H32" s="195"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="214" t="s">
         <v>144</v>
       </c>
-      <c r="B35" s="215"/>
-      <c r="C35" s="215"/>
-      <c r="D35" s="215"/>
-      <c r="E35" s="215"/>
-      <c r="F35" s="215"/>
-      <c r="G35" s="215"/>
-      <c r="H35" s="216"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="196" t="s">
+      <c r="B33" s="215"/>
+      <c r="C33" s="215"/>
+      <c r="D33" s="215"/>
+      <c r="E33" s="215"/>
+      <c r="F33" s="215"/>
+      <c r="G33" s="215"/>
+      <c r="H33" s="216"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="196" t="s">
         <v>145</v>
       </c>
-      <c r="B36" s="197"/>
-      <c r="C36" s="197"/>
-      <c r="D36" s="197"/>
-      <c r="E36" s="197"/>
-      <c r="F36" s="197"/>
-      <c r="G36" s="197"/>
-      <c r="H36" s="198">
-        <v>14622.12</v>
-      </c>
-      <c r="J36" s="11"/>
-    </row>
-    <row r="37" spans="1:14" s="12" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="170" t="s">
+      <c r="B34" s="197"/>
+      <c r="C34" s="197"/>
+      <c r="D34" s="197"/>
+      <c r="E34" s="197"/>
+      <c r="F34" s="197"/>
+      <c r="G34" s="197"/>
+      <c r="H34" s="198">
+        <v>20500.830000000002</v>
+      </c>
+      <c r="J34" s="11"/>
+    </row>
+    <row r="35" spans="1:11" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="170" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="171"/>
-      <c r="C37" s="171"/>
-      <c r="D37" s="171"/>
-      <c r="E37" s="171"/>
-      <c r="F37" s="171"/>
-      <c r="G37" s="171"/>
-      <c r="H37" s="172">
-        <f>H18+H23+H29+H33+H36</f>
-        <v>1735792.4900000002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A38" s="173" t="s">
+      <c r="B35" s="171"/>
+      <c r="C35" s="171"/>
+      <c r="D35" s="171"/>
+      <c r="E35" s="171"/>
+      <c r="F35" s="171"/>
+      <c r="G35" s="171"/>
+      <c r="H35" s="172">
+        <f>H18+H23+H27+H31+H34</f>
+        <v>2011840.7100000004</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="173" t="s">
         <v>154</v>
       </c>
-      <c r="B38" s="174"/>
-      <c r="C38" s="174"/>
-      <c r="D38" s="174"/>
-      <c r="E38" s="174"/>
-      <c r="F38" s="174"/>
-      <c r="G38" s="174"/>
-      <c r="H38" s="175"/>
-    </row>
-    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="204" t="s">
+      <c r="B36" s="174"/>
+      <c r="C36" s="174"/>
+      <c r="D36" s="174"/>
+      <c r="E36" s="174"/>
+      <c r="F36" s="174"/>
+      <c r="G36" s="174"/>
+      <c r="H36" s="175"/>
+    </row>
+    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="204" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="205"/>
-      <c r="C39" s="205"/>
-      <c r="D39" s="205"/>
-      <c r="E39" s="205"/>
-      <c r="F39" s="205"/>
-      <c r="G39" s="205"/>
-      <c r="H39" s="206"/>
-      <c r="I39" s="134"/>
-      <c r="K39" s="134"/>
-    </row>
-    <row r="40" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="207"/>
-      <c r="B40" s="208"/>
-      <c r="C40" s="208"/>
-      <c r="D40" s="208"/>
-      <c r="E40" s="208"/>
-      <c r="F40" s="208"/>
-      <c r="G40" s="208"/>
-      <c r="H40" s="209"/>
-    </row>
-    <row r="41" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="217"/>
-      <c r="B41" s="218"/>
-      <c r="C41" s="218"/>
-      <c r="D41" s="218"/>
-      <c r="E41" s="218"/>
-      <c r="F41" s="218"/>
-      <c r="G41" s="219"/>
-      <c r="H41" s="19"/>
-    </row>
-    <row r="42" spans="1:14" s="10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="220" t="s">
+      <c r="B37" s="205"/>
+      <c r="C37" s="205"/>
+      <c r="D37" s="205"/>
+      <c r="E37" s="205"/>
+      <c r="F37" s="205"/>
+      <c r="G37" s="205"/>
+      <c r="H37" s="206"/>
+      <c r="I37" s="134"/>
+      <c r="K37" s="134"/>
+    </row>
+    <row r="38" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="207"/>
+      <c r="B38" s="208"/>
+      <c r="C38" s="208"/>
+      <c r="D38" s="208"/>
+      <c r="E38" s="208"/>
+      <c r="F38" s="208"/>
+      <c r="G38" s="208"/>
+      <c r="H38" s="209"/>
+    </row>
+    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="217"/>
+      <c r="B39" s="218"/>
+      <c r="C39" s="218"/>
+      <c r="D39" s="218"/>
+      <c r="E39" s="218"/>
+      <c r="F39" s="218"/>
+      <c r="G39" s="219"/>
+      <c r="H39" s="19"/>
+    </row>
+    <row r="40" spans="1:11" s="10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="220" t="s">
         <v>16</v>
       </c>
-      <c r="B42" s="221"/>
-      <c r="C42" s="221"/>
-      <c r="D42" s="221"/>
-      <c r="E42" s="221"/>
-      <c r="F42" s="221"/>
-      <c r="G42" s="222"/>
-      <c r="H42" s="20">
-        <f>SUM(H41:H41)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" s="10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="150"/>
-      <c r="B43" s="150"/>
-      <c r="C43" s="150"/>
-      <c r="D43" s="150"/>
-      <c r="E43" s="150"/>
-      <c r="F43" s="150"/>
-      <c r="G43" s="150"/>
-      <c r="H43" s="151"/>
-    </row>
-    <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="221"/>
+      <c r="C40" s="221"/>
+      <c r="D40" s="221"/>
+      <c r="E40" s="221"/>
+      <c r="F40" s="221"/>
+      <c r="G40" s="222"/>
+      <c r="H40" s="20">
+        <f>SUM(H39:H39)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" s="10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="150"/>
+      <c r="B41" s="150"/>
+      <c r="C41" s="150"/>
+      <c r="D41" s="150"/>
+      <c r="E41" s="150"/>
+      <c r="F41" s="150"/>
+      <c r="G41" s="150"/>
+      <c r="H41" s="151"/>
+    </row>
+    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H42" s="14"/>
+      <c r="J42" s="11"/>
+    </row>
+    <row r="43" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="202" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" s="202"/>
+      <c r="C43" s="202"/>
+      <c r="D43" s="202"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="202"/>
+      <c r="G43" s="202"/>
+      <c r="H43" s="18">
+        <f>+H35+H36</f>
+        <v>2011840.7100000004</v>
+      </c>
+      <c r="J43" s="134"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="14"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
       <c r="H44" s="14"/>
-      <c r="J44" s="11"/>
-    </row>
-    <row r="45" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="202" t="s">
-        <v>129</v>
-      </c>
-      <c r="B45" s="202"/>
-      <c r="C45" s="202"/>
-      <c r="D45" s="202"/>
-      <c r="E45" s="202"/>
-      <c r="F45" s="202"/>
-      <c r="G45" s="202"/>
-      <c r="H45" s="18">
-        <f>+H37+H38</f>
-        <v>1735792.4900000002</v>
-      </c>
-      <c r="J45" s="134"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="21">
+        <f>H40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="14"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -2798,60 +2795,62 @@
       <c r="G46" s="14"/>
       <c r="H46" s="14"/>
     </row>
-    <row r="47" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="21">
-        <f>H42</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="14"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-    </row>
-    <row r="49" spans="1:10" ht="18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="210" t="s">
+    <row r="47" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="210" t="s">
         <v>13</v>
       </c>
-      <c r="B49" s="211"/>
-      <c r="C49" s="211"/>
-      <c r="D49" s="211"/>
-      <c r="E49" s="211"/>
-      <c r="F49" s="211"/>
-      <c r="G49" s="211"/>
-      <c r="H49" s="212"/>
-    </row>
-    <row r="50" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="203" t="s">
+      <c r="B47" s="211"/>
+      <c r="C47" s="211"/>
+      <c r="D47" s="211"/>
+      <c r="E47" s="211"/>
+      <c r="F47" s="211"/>
+      <c r="G47" s="211"/>
+      <c r="H47" s="212"/>
+    </row>
+    <row r="48" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="203" t="s">
         <v>135</v>
       </c>
-      <c r="B50" s="203"/>
-      <c r="C50" s="203"/>
-      <c r="D50" s="203"/>
-      <c r="E50" s="203"/>
-      <c r="F50" s="203"/>
-      <c r="G50" s="203"/>
-      <c r="H50" s="27">
-        <v>1842211.5713207321</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B48" s="203"/>
+      <c r="C48" s="203"/>
+      <c r="D48" s="203"/>
+      <c r="E48" s="203"/>
+      <c r="F48" s="203"/>
+      <c r="G48" s="203"/>
+      <c r="H48" s="27">
+        <v>1535480.951320732</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B49" s="23"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="29">
+        <f>Planilla!H31</f>
+        <v>1981241.3299999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" s="23"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="160"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B51" s="23"/>
       <c r="C51" s="23"/>
@@ -2859,69 +2858,48 @@
       <c r="E51" s="23"/>
       <c r="F51" s="23"/>
       <c r="G51" s="23"/>
-      <c r="H51" s="29">
-        <f>Planilla!H31</f>
-        <v>1360767.85</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="160"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="B53" s="23"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="23"/>
-      <c r="G53" s="23"/>
-      <c r="H53" s="24">
-        <f>-(H37+H42)</f>
-        <v>-1735792.4900000002</v>
-      </c>
+      <c r="H51" s="24">
+        <f>-(H35+H40)</f>
+        <v>-2011840.7100000004</v>
+      </c>
+      <c r="J51" s="11"/>
+    </row>
+    <row r="52" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A52" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="30">
+        <f>SUM(H48:H51)</f>
+        <v>1504881.5713207317</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J53" s="11"/>
     </row>
-    <row r="54" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A54" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B54" s="26"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="30">
-        <f>SUM(H50:H53)</f>
-        <v>1467186.931320732</v>
-      </c>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J54" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="D6:H8"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A50:G50"/>
-    <mergeCell ref="A39:H40"/>
-    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A37:H38"/>
+    <mergeCell ref="A47:H47"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="95" orientation="portrait" r:id="rId1"/>
@@ -2935,28 +2913,28 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.44140625" style="31" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="22.109375" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" style="33" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" style="32" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" style="32" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" style="32" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.88671875" customWidth="1"/>
-    <col min="12" max="12" width="13.88671875" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
-    <col min="14" max="14" width="11.88671875" customWidth="1"/>
-    <col min="15" max="15" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" style="31" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" style="33" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" style="32" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="32" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" style="32" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="12" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="224" t="str">
         <f>Gastos!E9</f>
         <v xml:space="preserve">PERIODO: MARZO </v>
@@ -2977,10 +2955,10 @@
       <c r="O1" s="225"/>
       <c r="P1" s="226"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="64"/>
       <c r="C2" s="147">
-        <v>1667498.4700000002</v>
+        <v>2011840.7100000004</v>
       </c>
       <c r="F2" s="244" t="s">
         <v>152</v>
@@ -2998,10 +2976,10 @@
       <c r="O2" s="235"/>
       <c r="P2" s="236"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="61"/>
       <c r="D3" s="147">
-        <v>974869.58</v>
+        <v>1143139.0900000001</v>
       </c>
       <c r="F3" s="247"/>
       <c r="G3" s="248"/>
@@ -3015,7 +2993,7 @@
       <c r="O3" s="238"/>
       <c r="P3" s="239"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="61"/>
       <c r="C4" s="243" t="s">
         <v>141</v>
@@ -3033,12 +3011,12 @@
       <c r="O4" s="238"/>
       <c r="P4" s="239"/>
     </row>
-    <row r="5" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="61"/>
       <c r="B5" s="63"/>
       <c r="C5" s="232">
         <f>D3</f>
-        <v>974869.58</v>
+        <v>1143139.0900000001</v>
       </c>
       <c r="D5" s="232"/>
       <c r="E5" s="9"/>
@@ -3054,7 +3032,7 @@
       <c r="O5" s="238"/>
       <c r="P5" s="239"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="61"/>
       <c r="C6" s="9" t="s">
         <v>140</v>
@@ -3075,12 +3053,12 @@
       <c r="O6" s="238"/>
       <c r="P6" s="239"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="61"/>
       <c r="B7" s="60"/>
       <c r="C7" s="232">
         <f>C2-D3</f>
-        <v>692628.89000000025</v>
+        <v>868701.62000000034</v>
       </c>
       <c r="D7" s="232"/>
       <c r="E7" s="62"/>
@@ -3096,7 +3074,7 @@
       <c r="O7" s="238"/>
       <c r="P7" s="239"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="61"/>
       <c r="B8" s="60"/>
       <c r="C8" s="60" t="s">
@@ -3116,7 +3094,7 @@
       <c r="O8" s="238"/>
       <c r="P8" s="239"/>
     </row>
-    <row r="9" spans="1:17" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="59"/>
       <c r="B9" s="58"/>
       <c r="C9" s="233">
@@ -3136,7 +3114,7 @@
       <c r="O9" s="241"/>
       <c r="P9" s="242"/>
     </row>
-    <row r="10" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="56" t="s">
         <v>29</v>
       </c>
@@ -3187,7 +3165,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="141" t="s">
         <v>66</v>
       </c>
@@ -3203,11 +3181,11 @@
         <v>7.9</v>
       </c>
       <c r="G11" s="154">
-        <v>186804.01</v>
+        <v>131732.01</v>
       </c>
       <c r="H11" s="154">
         <f>G11</f>
-        <v>186804.01</v>
+        <v>131732.01</v>
       </c>
       <c r="I11" s="45">
         <f>G11-H11</f>
@@ -3223,7 +3201,7 @@
       </c>
       <c r="L11" s="45">
         <f t="shared" ref="L11:L29" si="0">C$7*F11/100</f>
-        <v>54717.682310000026</v>
+        <v>68627.427980000037</v>
       </c>
       <c r="M11" s="45">
         <f t="shared" ref="M11:M29" si="1">C$9*F11/100</f>
@@ -3231,21 +3209,21 @@
       </c>
       <c r="N11" s="45">
         <f t="shared" ref="N11:N22" si="2">C$5*F11/100</f>
-        <v>77014.696819999997</v>
+        <v>90307.988110000006</v>
       </c>
       <c r="O11" s="154">
         <f>ROUND(L11+K11+M11+N11,0) + Q11</f>
-        <v>131732.01</v>
+        <v>158935.01</v>
       </c>
       <c r="P11" s="153">
         <f>ROUND(O11+O11*3%,0) + Q11</f>
-        <v>135684.01</v>
+        <v>163703.01</v>
       </c>
       <c r="Q11" s="28">
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="135" t="s">
         <v>67</v>
       </c>
@@ -3261,27 +3239,24 @@
         <v>7.9</v>
       </c>
       <c r="G12" s="157">
-        <v>190951.02</v>
-      </c>
-      <c r="H12" s="154">
-        <f>G12</f>
-        <v>190951.02</v>
-      </c>
+        <v>131732.01999999999</v>
+      </c>
+      <c r="H12" s="154"/>
       <c r="I12" s="45">
         <f t="shared" ref="I12:I29" si="3">G12-H12</f>
-        <v>0</v>
+        <v>131732.01999999999</v>
       </c>
       <c r="J12" s="146">
         <f t="shared" ref="J12:J29" si="4">(I12)*3%</f>
-        <v>0</v>
+        <v>3951.9605999999994</v>
       </c>
       <c r="K12" s="146">
         <f t="shared" ref="K12:K29" si="5">I12+J12</f>
-        <v>0</v>
+        <v>135683.98059999998</v>
       </c>
       <c r="L12" s="127">
         <f t="shared" si="0"/>
-        <v>54717.682310000026</v>
+        <v>68627.427980000037</v>
       </c>
       <c r="M12" s="45">
         <f t="shared" si="1"/>
@@ -3289,22 +3264,22 @@
       </c>
       <c r="N12" s="45">
         <f t="shared" si="2"/>
-        <v>77014.696819999997</v>
+        <v>90307.988110000006</v>
       </c>
       <c r="O12" s="154">
         <f t="shared" ref="O12:O29" si="6">ROUND(L12+K12+M12+N12,0) + Q12</f>
-        <v>131732.01999999999</v>
+        <v>294619.02</v>
       </c>
       <c r="P12" s="153">
         <f t="shared" ref="P12:P29" si="7">ROUND(O12+O12*3%,0) + Q12</f>
-        <v>135684.01999999999</v>
+        <v>303458.02</v>
       </c>
       <c r="Q12" s="28">
         <f t="shared" ref="Q12:Q29" si="8">Q11+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="128" t="s">
         <v>68</v>
       </c>
@@ -3322,24 +3297,26 @@
         <v>7.9</v>
       </c>
       <c r="G13" s="166">
-        <v>190951.03</v>
-      </c>
-      <c r="H13" s="166"/>
+        <v>328412.03000000003</v>
+      </c>
+      <c r="H13" s="166">
+        <v>131732.04</v>
+      </c>
       <c r="I13" s="168">
         <f t="shared" si="3"/>
-        <v>190951.03</v>
+        <v>196679.99000000002</v>
       </c>
       <c r="J13" s="179">
         <f t="shared" si="4"/>
-        <v>5728.5308999999997</v>
+        <v>5900.3996999999999</v>
       </c>
       <c r="K13" s="179">
         <f t="shared" si="5"/>
-        <v>196679.56090000001</v>
+        <v>202580.38970000003</v>
       </c>
       <c r="L13" s="167">
         <f t="shared" si="0"/>
-        <v>54717.682310000026</v>
+        <v>68627.427980000037</v>
       </c>
       <c r="M13" s="168">
         <f t="shared" si="1"/>
@@ -3347,22 +3324,22 @@
       </c>
       <c r="N13" s="168">
         <f t="shared" si="2"/>
-        <v>77014.696819999997</v>
+        <v>90307.988110000006</v>
       </c>
       <c r="O13" s="166">
         <f t="shared" si="6"/>
-        <v>328412.03000000003</v>
+        <v>361516.03</v>
       </c>
       <c r="P13" s="169">
         <f t="shared" si="7"/>
-        <v>338264.03</v>
+        <v>372362.03</v>
       </c>
       <c r="Q13" s="28">
         <f t="shared" si="8"/>
         <v>0.03</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="80" t="s">
         <v>69</v>
       </c>
@@ -3378,27 +3355,26 @@
         <v>7.9</v>
       </c>
       <c r="G14" s="158">
-        <v>190951.04000000001</v>
+        <v>131732.04</v>
       </c>
       <c r="H14" s="154">
-        <f>G14</f>
-        <v>190951.04000000001</v>
+        <v>135684.04</v>
       </c>
       <c r="I14" s="45">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-3952</v>
       </c>
       <c r="J14" s="146">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-118.56</v>
       </c>
       <c r="K14" s="146">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4070.56</v>
       </c>
       <c r="L14" s="43">
         <f t="shared" si="0"/>
-        <v>54717.682310000026</v>
+        <v>68627.427980000037</v>
       </c>
       <c r="M14" s="45">
         <f t="shared" si="1"/>
@@ -3406,22 +3382,22 @@
       </c>
       <c r="N14" s="45">
         <f t="shared" si="2"/>
-        <v>77014.696819999997</v>
+        <v>90307.988110000006</v>
       </c>
       <c r="O14" s="154">
         <f t="shared" si="6"/>
-        <v>131732.04</v>
+        <v>154865.04</v>
       </c>
       <c r="P14" s="153">
         <f t="shared" si="7"/>
-        <v>135684.04</v>
+        <v>159511.04000000001</v>
       </c>
       <c r="Q14" s="28">
         <f t="shared" si="8"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="80" t="s">
         <v>70</v>
       </c>
@@ -3437,24 +3413,27 @@
         <v>7.9</v>
       </c>
       <c r="G15" s="154">
-        <v>186706.05</v>
-      </c>
-      <c r="H15" s="154"/>
+        <v>324040.05</v>
+      </c>
+      <c r="H15" s="154">
+        <f>G15</f>
+        <v>324040.05</v>
+      </c>
       <c r="I15" s="45">
         <f t="shared" si="3"/>
-        <v>186706.05</v>
+        <v>0</v>
       </c>
       <c r="J15" s="146">
         <f t="shared" si="4"/>
-        <v>5601.1814999999997</v>
+        <v>0</v>
       </c>
       <c r="K15" s="146">
         <f t="shared" si="5"/>
-        <v>192307.23149999999</v>
+        <v>0</v>
       </c>
       <c r="L15" s="127">
         <f t="shared" si="0"/>
-        <v>54717.682310000026</v>
+        <v>68627.427980000037</v>
       </c>
       <c r="M15" s="45">
         <f t="shared" si="1"/>
@@ -3462,22 +3441,22 @@
       </c>
       <c r="N15" s="45">
         <f t="shared" si="2"/>
-        <v>77014.696819999997</v>
+        <v>90307.988110000006</v>
       </c>
       <c r="O15" s="154">
         <f t="shared" si="6"/>
-        <v>324040.05</v>
+        <v>158935.04999999999</v>
       </c>
       <c r="P15" s="153">
         <f t="shared" si="7"/>
-        <v>333761.05</v>
+        <v>163703.04999999999</v>
       </c>
       <c r="Q15" s="28">
         <f t="shared" si="8"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="128" t="s">
         <v>71</v>
       </c>
@@ -3495,11 +3474,11 @@
         <v>7.9</v>
       </c>
       <c r="G16" s="154">
-        <v>190951.06</v>
+        <v>131732.06</v>
       </c>
       <c r="H16" s="154">
         <f>G16</f>
-        <v>190951.06</v>
+        <v>131732.06</v>
       </c>
       <c r="I16" s="45">
         <f t="shared" si="3"/>
@@ -3515,7 +3494,7 @@
       </c>
       <c r="L16" s="127">
         <f t="shared" si="0"/>
-        <v>54717.682310000026</v>
+        <v>68627.427980000037</v>
       </c>
       <c r="M16" s="45">
         <f t="shared" si="1"/>
@@ -3523,22 +3502,22 @@
       </c>
       <c r="N16" s="45">
         <f t="shared" si="2"/>
-        <v>77014.696819999997</v>
+        <v>90307.988110000006</v>
       </c>
       <c r="O16" s="154">
         <f t="shared" si="6"/>
-        <v>131732.06</v>
+        <v>158935.06</v>
       </c>
       <c r="P16" s="153">
         <f t="shared" si="7"/>
-        <v>135684.06</v>
+        <v>163703.06</v>
       </c>
       <c r="Q16" s="28">
         <f t="shared" si="8"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="80" t="s">
         <v>72</v>
       </c>
@@ -3556,11 +3535,11 @@
         <v>7.9</v>
       </c>
       <c r="G17" s="154">
-        <v>190951.07</v>
+        <v>131732.07</v>
       </c>
       <c r="H17" s="154">
         <f>G17</f>
-        <v>190951.07</v>
+        <v>131732.07</v>
       </c>
       <c r="I17" s="45">
         <f t="shared" si="3"/>
@@ -3576,7 +3555,7 @@
       </c>
       <c r="L17" s="127">
         <f t="shared" si="0"/>
-        <v>54717.682310000026</v>
+        <v>68627.427980000037</v>
       </c>
       <c r="M17" s="45">
         <f t="shared" si="1"/>
@@ -3584,22 +3563,22 @@
       </c>
       <c r="N17" s="45">
         <f t="shared" si="2"/>
-        <v>77014.696819999997</v>
+        <v>90307.988110000006</v>
       </c>
       <c r="O17" s="154">
         <f t="shared" si="6"/>
-        <v>131732.07</v>
+        <v>158935.07</v>
       </c>
       <c r="P17" s="153">
         <f t="shared" si="7"/>
-        <v>135684.07</v>
+        <v>163703.07</v>
       </c>
       <c r="Q17" s="28">
         <f t="shared" si="8"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="128" t="s">
         <v>73</v>
       </c>
@@ -3617,24 +3596,27 @@
         <v>7.9</v>
       </c>
       <c r="G18" s="154">
-        <v>190951.08</v>
-      </c>
-      <c r="H18" s="154"/>
+        <v>328412.08</v>
+      </c>
+      <c r="H18" s="154">
+        <f>G18</f>
+        <v>328412.08</v>
+      </c>
       <c r="I18" s="45">
         <f t="shared" si="3"/>
-        <v>190951.08</v>
+        <v>0</v>
       </c>
       <c r="J18" s="146">
         <f t="shared" si="4"/>
-        <v>5728.5323999999991</v>
+        <v>0</v>
       </c>
       <c r="K18" s="146">
         <f t="shared" si="5"/>
-        <v>196679.61239999998</v>
+        <v>0</v>
       </c>
       <c r="L18" s="127">
         <f t="shared" si="0"/>
-        <v>54717.682310000026</v>
+        <v>68627.427980000037</v>
       </c>
       <c r="M18" s="45">
         <f t="shared" si="1"/>
@@ -3642,22 +3624,22 @@
       </c>
       <c r="N18" s="45">
         <f t="shared" si="2"/>
-        <v>77014.696819999997</v>
+        <v>90307.988110000006</v>
       </c>
       <c r="O18" s="154">
         <f t="shared" si="6"/>
-        <v>328412.08</v>
+        <v>158935.07999999999</v>
       </c>
       <c r="P18" s="153">
         <f t="shared" si="7"/>
-        <v>338264.08</v>
+        <v>163703.07999999999</v>
       </c>
       <c r="Q18" s="28">
         <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="128" t="s">
         <v>74</v>
       </c>
@@ -3673,27 +3655,26 @@
         <v>7.9</v>
       </c>
       <c r="G19" s="154">
-        <v>186706.09</v>
+        <v>131732.09</v>
       </c>
       <c r="H19" s="154">
-        <f>G19</f>
-        <v>186706.09</v>
+        <v>135681.09</v>
       </c>
       <c r="I19" s="45">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-3949</v>
       </c>
       <c r="J19" s="146">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-118.47</v>
       </c>
       <c r="K19" s="146">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4067.47</v>
       </c>
       <c r="L19" s="127">
         <f t="shared" si="0"/>
-        <v>54717.682310000026</v>
+        <v>68627.427980000037</v>
       </c>
       <c r="M19" s="45">
         <f t="shared" si="1"/>
@@ -3701,22 +3682,22 @@
       </c>
       <c r="N19" s="45">
         <f t="shared" si="2"/>
-        <v>77014.696819999997</v>
+        <v>90307.988110000006</v>
       </c>
       <c r="O19" s="154">
         <f t="shared" si="6"/>
-        <v>131732.09</v>
+        <v>154868.09</v>
       </c>
       <c r="P19" s="153">
         <f t="shared" si="7"/>
-        <v>135684.09</v>
+        <v>159514.09</v>
       </c>
       <c r="Q19" s="28">
         <f t="shared" si="8"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="161" t="s">
         <v>75</v>
       </c>
@@ -3732,27 +3713,26 @@
         <v>7.9</v>
       </c>
       <c r="G20" s="154">
-        <v>190951.1</v>
+        <v>131732.1</v>
       </c>
       <c r="H20" s="154">
-        <f>G20</f>
-        <v>190951.1</v>
+        <v>135681.1</v>
       </c>
       <c r="I20" s="45">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-3949</v>
       </c>
       <c r="J20" s="146">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-118.47</v>
       </c>
       <c r="K20" s="146">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4067.47</v>
       </c>
       <c r="L20" s="127">
         <f t="shared" si="0"/>
-        <v>54717.682310000026</v>
+        <v>68627.427980000037</v>
       </c>
       <c r="M20" s="45">
         <f t="shared" si="1"/>
@@ -3760,15 +3740,15 @@
       </c>
       <c r="N20" s="45">
         <f t="shared" si="2"/>
-        <v>77014.696819999997</v>
+        <v>90307.988110000006</v>
       </c>
       <c r="O20" s="154">
         <f t="shared" si="6"/>
-        <v>131732.1</v>
+        <v>154868.1</v>
       </c>
       <c r="P20" s="153">
         <f t="shared" si="7"/>
-        <v>135684.1</v>
+        <v>159514.1</v>
       </c>
       <c r="Q20" s="156">
         <f t="shared" si="8"/>
@@ -3776,7 +3756,7 @@
       </c>
       <c r="R20" s="10"/>
     </row>
-    <row r="21" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="161" t="s">
         <v>76</v>
       </c>
@@ -3794,24 +3774,27 @@
         <v>7.9</v>
       </c>
       <c r="G21" s="166">
-        <v>183618.11</v>
-      </c>
-      <c r="H21" s="166"/>
+        <v>330485.11</v>
+      </c>
+      <c r="H21" s="166">
+        <f>346878-H24</f>
+        <v>330484.86</v>
+      </c>
       <c r="I21" s="168">
         <f t="shared" si="3"/>
-        <v>183618.11</v>
+        <v>0.25</v>
       </c>
       <c r="J21" s="179">
         <f t="shared" si="4"/>
-        <v>5508.5432999999994</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="K21" s="179">
         <f t="shared" si="5"/>
-        <v>189126.65329999998</v>
+        <v>0.25750000000000001</v>
       </c>
       <c r="L21" s="167">
         <f t="shared" si="0"/>
-        <v>54717.682310000026</v>
+        <v>68627.427980000037</v>
       </c>
       <c r="M21" s="168">
         <f t="shared" si="1"/>
@@ -3819,22 +3802,22 @@
       </c>
       <c r="N21" s="168">
         <f t="shared" si="2"/>
-        <v>77014.696819999997</v>
+        <v>90307.988110000006</v>
       </c>
       <c r="O21" s="166">
         <f t="shared" si="6"/>
-        <v>320859.11</v>
+        <v>158936.10999999999</v>
       </c>
       <c r="P21" s="169">
         <f t="shared" si="7"/>
-        <v>330485.11</v>
+        <v>163704.10999999999</v>
       </c>
       <c r="Q21" s="28">
         <f t="shared" si="8"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="128" t="s">
         <v>77</v>
       </c>
@@ -3852,24 +3835,24 @@
         <v>7.9</v>
       </c>
       <c r="G22" s="166">
-        <v>190951.12</v>
+        <v>328412.12</v>
       </c>
       <c r="H22" s="166"/>
       <c r="I22" s="168">
         <f t="shared" si="3"/>
-        <v>190951.12</v>
+        <v>328412.12</v>
       </c>
       <c r="J22" s="179">
         <f t="shared" si="4"/>
-        <v>5728.5335999999998</v>
+        <v>9852.3635999999988</v>
       </c>
       <c r="K22" s="179">
         <f t="shared" si="5"/>
-        <v>196679.65359999999</v>
+        <v>338264.48359999998</v>
       </c>
       <c r="L22" s="167">
         <f t="shared" si="0"/>
-        <v>54717.682310000026</v>
+        <v>68627.427980000037</v>
       </c>
       <c r="M22" s="168">
         <f t="shared" si="1"/>
@@ -3877,15 +3860,15 @@
       </c>
       <c r="N22" s="168">
         <f t="shared" si="2"/>
-        <v>77014.696819999997</v>
+        <v>90307.988110000006</v>
       </c>
       <c r="O22" s="166">
         <f t="shared" si="6"/>
-        <v>328412.12</v>
+        <v>497200.12</v>
       </c>
       <c r="P22" s="169">
         <f t="shared" si="7"/>
-        <v>338264.12</v>
+        <v>512116.12</v>
       </c>
       <c r="Q22" s="28">
         <f t="shared" si="8"/>
@@ -3895,7 +3878,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="128"/>
       <c r="B23" s="129"/>
       <c r="C23" s="66" t="s">
@@ -3912,11 +3895,11 @@
         <v>0.74</v>
       </c>
       <c r="G23" s="154">
-        <v>10834.13</v>
+        <v>5125.13</v>
       </c>
       <c r="H23" s="154">
         <f>G23</f>
-        <v>10834.13</v>
+        <v>5125.13</v>
       </c>
       <c r="I23" s="45">
         <f t="shared" si="3"/>
@@ -3932,7 +3915,7 @@
       </c>
       <c r="L23" s="127">
         <f t="shared" si="0"/>
-        <v>5125.4537860000019</v>
+        <v>6428.3919880000021</v>
       </c>
       <c r="M23" s="45">
         <f t="shared" si="1"/>
@@ -3941,18 +3924,18 @@
       <c r="N23" s="127"/>
       <c r="O23" s="154">
         <f t="shared" si="6"/>
-        <v>5125.13</v>
+        <v>6428.13</v>
       </c>
       <c r="P23" s="153">
         <f t="shared" si="7"/>
-        <v>5279.13</v>
+        <v>6621.13</v>
       </c>
       <c r="Q23" s="28">
         <f t="shared" si="8"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="161"/>
       <c r="B24" s="129"/>
       <c r="C24" s="162" t="s">
@@ -3969,24 +3952,27 @@
         <v>0.74</v>
       </c>
       <c r="G24" s="166">
-        <v>10475.14</v>
-      </c>
-      <c r="H24" s="166"/>
+        <v>16393.14</v>
+      </c>
+      <c r="H24" s="166">
+        <f>G24</f>
+        <v>16393.14</v>
+      </c>
       <c r="I24" s="168">
         <f t="shared" si="3"/>
-        <v>10475.14</v>
+        <v>0</v>
       </c>
       <c r="J24" s="179">
         <f t="shared" si="4"/>
-        <v>314.25419999999997</v>
+        <v>0</v>
       </c>
       <c r="K24" s="179">
         <f t="shared" si="5"/>
-        <v>10789.394199999999</v>
+        <v>0</v>
       </c>
       <c r="L24" s="167">
         <f t="shared" si="0"/>
-        <v>5125.4537860000019</v>
+        <v>6428.3919880000021</v>
       </c>
       <c r="M24" s="168">
         <f t="shared" si="1"/>
@@ -3998,18 +3984,18 @@
       </c>
       <c r="O24" s="166">
         <f t="shared" si="6"/>
-        <v>15915.14</v>
+        <v>6428.14</v>
       </c>
       <c r="P24" s="169">
         <f t="shared" si="7"/>
-        <v>16393.14</v>
+        <v>6621.14</v>
       </c>
       <c r="Q24" s="28">
         <f t="shared" si="8"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="128"/>
       <c r="B25" s="129"/>
       <c r="C25" s="66" t="s">
@@ -4024,27 +4010,26 @@
         <v>0.74</v>
       </c>
       <c r="G25" s="154">
-        <v>10834.15</v>
+        <v>5125.1499999999996</v>
       </c>
       <c r="H25" s="154">
-        <f>G25</f>
-        <v>10834.15</v>
+        <v>5279.15</v>
       </c>
       <c r="I25" s="45">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-154</v>
       </c>
       <c r="J25" s="146">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-4.62</v>
       </c>
       <c r="K25" s="146">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-158.62</v>
       </c>
       <c r="L25" s="127">
         <f t="shared" si="0"/>
-        <v>5125.4537860000019</v>
+        <v>6428.3919880000021</v>
       </c>
       <c r="M25" s="45">
         <f t="shared" si="1"/>
@@ -4056,11 +4041,11 @@
       </c>
       <c r="O25" s="154">
         <f t="shared" si="6"/>
-        <v>5125.1499999999996</v>
+        <v>6270.15</v>
       </c>
       <c r="P25" s="153">
         <f t="shared" si="7"/>
-        <v>5279.15</v>
+        <v>6458.15</v>
       </c>
       <c r="Q25" s="176">
         <f t="shared" si="8"/>
@@ -4068,7 +4053,7 @@
       </c>
       <c r="R25" s="10"/>
     </row>
-    <row r="26" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="128"/>
       <c r="B26" s="126"/>
       <c r="C26" s="66" t="s">
@@ -4085,24 +4070,27 @@
         <v>0.74</v>
       </c>
       <c r="G26" s="154">
-        <v>10834.16</v>
-      </c>
-      <c r="H26" s="154"/>
+        <v>16285.16</v>
+      </c>
+      <c r="H26" s="154">
+        <f>G26</f>
+        <v>16285.16</v>
+      </c>
       <c r="I26" s="45">
         <f t="shared" si="3"/>
-        <v>10834.16</v>
+        <v>0</v>
       </c>
       <c r="J26" s="146">
         <f t="shared" si="4"/>
-        <v>325.02479999999997</v>
+        <v>0</v>
       </c>
       <c r="K26" s="146">
         <f t="shared" si="5"/>
-        <v>11159.184799999999</v>
+        <v>0</v>
       </c>
       <c r="L26" s="127">
         <f t="shared" si="0"/>
-        <v>5125.4537860000019</v>
+        <v>6428.3919880000021</v>
       </c>
       <c r="M26" s="45">
         <f t="shared" si="1"/>
@@ -4114,18 +4102,18 @@
       </c>
       <c r="O26" s="154">
         <f t="shared" si="6"/>
-        <v>16285.16</v>
+        <v>6428.16</v>
       </c>
       <c r="P26" s="153">
         <f t="shared" si="7"/>
-        <v>16774.16</v>
+        <v>6621.16</v>
       </c>
       <c r="Q26" s="28">
         <f t="shared" si="8"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="80"/>
       <c r="B27" s="49"/>
       <c r="C27" s="65" t="s">
@@ -4140,24 +4128,27 @@
         <v>0.74</v>
       </c>
       <c r="G27" s="159">
-        <v>10676.17</v>
-      </c>
-      <c r="H27" s="154"/>
+        <v>16122.17</v>
+      </c>
+      <c r="H27" s="154">
+        <f>G27</f>
+        <v>16122.17</v>
+      </c>
       <c r="I27" s="45">
         <f t="shared" si="3"/>
-        <v>10676.17</v>
+        <v>0</v>
       </c>
       <c r="J27" s="146">
         <f t="shared" si="4"/>
-        <v>320.2851</v>
+        <v>0</v>
       </c>
       <c r="K27" s="146">
         <f t="shared" si="5"/>
-        <v>10996.455099999999</v>
+        <v>0</v>
       </c>
       <c r="L27" s="43">
         <f t="shared" si="0"/>
-        <v>5125.4537860000019</v>
+        <v>6428.3919880000021</v>
       </c>
       <c r="M27" s="45">
         <f t="shared" si="1"/>
@@ -4169,18 +4160,18 @@
       </c>
       <c r="O27" s="154">
         <f t="shared" si="6"/>
-        <v>16122.17</v>
+        <v>6428.17</v>
       </c>
       <c r="P27" s="153">
         <f t="shared" si="7"/>
-        <v>16606.169999999998</v>
+        <v>6621.17</v>
       </c>
       <c r="Q27" s="28">
         <f t="shared" si="8"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="148"/>
       <c r="B28" s="149"/>
       <c r="C28" s="66" t="s">
@@ -4197,11 +4188,11 @@
         <v>0.74</v>
       </c>
       <c r="G28" s="154">
-        <v>10834.18</v>
+        <v>5125.18</v>
       </c>
       <c r="H28" s="154">
         <f>G28</f>
-        <v>10834.18</v>
+        <v>5125.18</v>
       </c>
       <c r="I28" s="45">
         <f t="shared" si="3"/>
@@ -4217,7 +4208,7 @@
       </c>
       <c r="L28" s="45">
         <f t="shared" si="0"/>
-        <v>5125.4537860000019</v>
+        <v>6428.3919880000021</v>
       </c>
       <c r="M28" s="45">
         <f t="shared" si="1"/>
@@ -4229,18 +4220,18 @@
       </c>
       <c r="O28" s="154">
         <f t="shared" si="6"/>
-        <v>5125.18</v>
+        <v>6428.18</v>
       </c>
       <c r="P28" s="153">
         <f t="shared" si="7"/>
-        <v>5279.18</v>
+        <v>6621.18</v>
       </c>
       <c r="Q28" s="28">
         <f t="shared" si="8"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="128"/>
       <c r="B29" s="140"/>
       <c r="C29" s="66" t="s">
@@ -4257,24 +4248,24 @@
         <v>0.74</v>
       </c>
       <c r="G29" s="154">
-        <v>10834.19</v>
+        <v>16285.19</v>
       </c>
       <c r="H29" s="154"/>
       <c r="I29" s="45">
         <f t="shared" si="3"/>
-        <v>10834.19</v>
+        <v>16285.19</v>
       </c>
       <c r="J29" s="146">
         <f t="shared" si="4"/>
-        <v>325.02570000000003</v>
+        <v>488.5557</v>
       </c>
       <c r="K29" s="146">
         <f t="shared" si="5"/>
-        <v>11159.215700000001</v>
+        <v>16773.745699999999</v>
       </c>
       <c r="L29" s="127">
         <f t="shared" si="0"/>
-        <v>5125.4537860000019</v>
+        <v>6428.3919880000021</v>
       </c>
       <c r="M29" s="45">
         <f t="shared" si="1"/>
@@ -4286,18 +4277,18 @@
       </c>
       <c r="O29" s="154">
         <f t="shared" si="6"/>
-        <v>16285.19</v>
+        <v>23202.19</v>
       </c>
       <c r="P29" s="153">
         <f t="shared" si="7"/>
-        <v>16774.189999999999</v>
+        <v>23898.19</v>
       </c>
       <c r="Q29" s="28">
         <f t="shared" si="8"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="50"/>
       <c r="B30" s="49"/>
       <c r="C30" s="48"/>
@@ -4318,7 +4309,7 @@
       <c r="O30" s="44"/>
       <c r="P30" s="79"/>
     </row>
-    <row r="31" spans="1:19" s="36" customFormat="1" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:19" s="36" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="230"/>
       <c r="B31" s="231"/>
       <c r="C31" s="231"/>
@@ -4327,21 +4318,21 @@
       <c r="F31" s="68"/>
       <c r="G31" s="39">
         <f>SUM(G11:G30)</f>
-        <v>2346764.9000000008</v>
+        <v>2642346.9000000008</v>
       </c>
       <c r="H31" s="40">
         <f>SUM(H11:H30)</f>
-        <v>1360767.85</v>
+        <v>1981241.3299999998</v>
       </c>
       <c r="I31" s="40">
         <f>SUM(I11:I30)</f>
-        <v>985997.04999999993</v>
+        <v>661105.56999999995</v>
       </c>
       <c r="J31" s="38"/>
       <c r="K31" s="37"/>
       <c r="L31" s="40">
         <f>SUM(L11:L30)</f>
-        <v>692490.36422200047</v>
+        <v>868527.87967600056</v>
       </c>
       <c r="M31" s="40">
         <f>SUM(M11:M29)</f>
@@ -4349,19 +4340,19 @@
       </c>
       <c r="N31" s="40">
         <f>SUM(N11:N29)</f>
-        <v>924176.36183999979</v>
+        <v>1083695.8573200002</v>
       </c>
       <c r="O31" s="40">
         <f>SUM(O11:O29)</f>
-        <v>2632242.9000000008</v>
+        <v>2633160.9000000008</v>
       </c>
       <c r="P31" s="40">
         <f>SUM(P11:P29)</f>
-        <v>2711211.9000000008</v>
+        <v>2712156.9000000008</v>
       </c>
       <c r="S31"/>
     </row>
-    <row r="32" spans="1:19" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="227" t="s">
         <v>19</v>
       </c>
@@ -4380,7 +4371,7 @@
       <c r="O32" s="228"/>
       <c r="P32" s="229"/>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="F33" s="35"/>
       <c r="G33" s="34"/>
       <c r="H33" s="34"/>
@@ -4388,7 +4379,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="223"/>
       <c r="D34" s="223"/>
       <c r="E34" s="223"/>
@@ -4400,7 +4391,7 @@
       <c r="K34" s="223"/>
       <c r="L34" s="223"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="223"/>
       <c r="D35" s="223"/>
       <c r="E35" s="223"/>
@@ -4412,7 +4403,7 @@
       <c r="K35" s="223"/>
       <c r="L35" s="223"/>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C36" s="223"/>
       <c r="D36" s="223"/>
       <c r="E36" s="223"/>
@@ -4424,7 +4415,7 @@
       <c r="K36" s="223"/>
       <c r="L36" s="223"/>
     </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C37" s="223"/>
       <c r="D37" s="223"/>
       <c r="E37" s="223"/>
@@ -4436,7 +4427,7 @@
       <c r="K37" s="223"/>
       <c r="L37" s="223"/>
     </row>
-    <row r="38" spans="3:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="223"/>
       <c r="D38" s="223"/>
       <c r="E38" s="223"/>
@@ -4463,29 +4454,29 @@
     <mergeCell ref="F6:I9"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="66" fitToWidth="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="68" fitToWidth="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="83" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="83" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" style="83" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" style="83" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="83" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.44140625" style="83" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" style="83" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="83" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" style="83" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="83" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="83" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.42578125" style="83" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="83" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.44140625" style="83"/>
-    <col min="13" max="13" width="14.6640625" style="83" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5546875" style="83" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.44140625" style="83"/>
+    <col min="9" max="12" width="11.42578125" style="83"/>
+    <col min="13" max="13" width="14.7109375" style="83" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" style="83" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="262" t="s">
         <v>65</v>
       </c>
@@ -4494,7 +4485,7 @@
       <c r="D1" s="263"/>
       <c r="E1" s="264"/>
     </row>
-    <row r="2" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="124"/>
       <c r="B2" s="109"/>
       <c r="C2" s="109"/>
@@ -4503,7 +4494,7 @@
       </c>
       <c r="E2" s="120"/>
     </row>
-    <row r="3" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="122">
         <f>13+28+19</f>
         <v>60</v>
@@ -4525,28 +4516,28 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="119"/>
       <c r="B4" s="118"/>
       <c r="C4" s="118"/>
       <c r="D4" s="118"/>
       <c r="E4" s="117"/>
     </row>
-    <row r="5" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="116"/>
       <c r="B5" s="116"/>
       <c r="C5" s="116"/>
       <c r="D5" s="116"/>
       <c r="E5" s="116"/>
     </row>
-    <row r="6" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="116"/>
       <c r="B6" s="116"/>
       <c r="C6" s="116"/>
       <c r="D6" s="116"/>
       <c r="E6" s="116"/>
     </row>
-    <row r="7" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="265" t="s">
         <v>62</v>
       </c>
@@ -4564,7 +4555,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="77">
         <v>953033.85</v>
       </c>
@@ -4600,7 +4591,7 @@
         <v>2365.2600000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="112" t="s">
         <v>31</v>
       </c>
@@ -4649,7 +4640,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="110" t="s">
         <v>32</v>
       </c>
@@ -4698,7 +4689,7 @@
         <v>6.4240000000000005E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="110" t="s">
         <v>33</v>
       </c>
@@ -4746,7 +4737,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="110" t="s">
         <v>34</v>
       </c>
@@ -4793,7 +4784,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="110" t="s">
         <v>35</v>
       </c>
@@ -4836,7 +4827,7 @@
         <v>3266.9389024000006</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="110" t="s">
         <v>36</v>
       </c>
@@ -4871,7 +4862,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="110" t="s">
         <v>37</v>
       </c>
@@ -4910,7 +4901,7 @@
         <v>13227.0974549</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="110" t="s">
         <v>38</v>
       </c>
@@ -4945,7 +4936,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="110" t="s">
         <v>39</v>
       </c>
@@ -4980,7 +4971,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="110" t="s">
         <v>40</v>
       </c>
@@ -5015,7 +5006,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="110" t="s">
         <v>41</v>
       </c>
@@ -5050,7 +5041,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="110" t="s">
         <v>42</v>
       </c>
@@ -5082,7 +5073,7 @@
         <v>89551.274723634051</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="108" t="s">
         <v>124</v>
       </c>
@@ -5104,7 +5095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="70">
         <f>+D21/E8</f>
         <v>0.70190597204574334</v>
@@ -5114,7 +5105,7 @@
       </c>
       <c r="L22" s="103"/>
     </row>
-    <row r="23" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="69">
         <f>100%-A22</f>
         <v>0.29809402795425666</v>
@@ -5123,23 +5114,23 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="101"/>
       <c r="J25" s="83">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="J26" s="83">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="J27" s="83">
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B28" s="268" t="s">
         <v>123</v>
       </c>
@@ -5151,7 +5142,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B29" s="100" t="s">
         <v>122</v>
       </c>
@@ -5171,7 +5162,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B30" s="94" t="s">
         <v>117</v>
       </c>
@@ -5194,7 +5185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B31" s="94" t="s">
         <v>116</v>
       </c>
@@ -5213,7 +5204,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B32" s="94" t="s">
         <v>115</v>
       </c>
@@ -5232,7 +5223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B33" s="94" t="s">
         <v>114</v>
       </c>
@@ -5255,7 +5246,7 @@
         <v>0.31000000000130967</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B34" s="94" t="s">
         <v>113</v>
       </c>
@@ -5274,7 +5265,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B35" s="94" t="s">
         <v>112</v>
       </c>
@@ -5293,7 +5284,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B36" s="94" t="s">
         <v>111</v>
       </c>
@@ -5312,7 +5303,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B37" s="94" t="s">
         <v>110</v>
       </c>
@@ -5328,7 +5319,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B38" s="94" t="s">
         <v>109</v>
       </c>
@@ -5350,7 +5341,7 @@
         <v>-11.950000000000003</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B39" s="94" t="s">
         <v>107</v>
       </c>
@@ -5364,7 +5355,7 @@
         <v>36500</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B40" s="94" t="s">
         <v>106</v>
       </c>
@@ -5378,7 +5369,7 @@
         <v>40500</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B41" s="94" t="s">
         <v>105</v>
       </c>
@@ -5392,7 +5383,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="42" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B42" s="94" t="s">
         <v>104</v>
       </c>
@@ -5406,7 +5397,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B43" s="94" t="s">
         <v>103</v>
       </c>
@@ -5420,7 +5411,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="44" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B44" s="91" t="s">
         <v>102</v>
       </c>
@@ -5434,7 +5425,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B45" s="91" t="s">
         <v>101</v>
       </c>
@@ -5448,7 +5439,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B46" s="91" t="s">
         <v>100</v>
       </c>
@@ -5462,7 +5453,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="87" t="s">
         <v>99</v>
       </c>
